--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sev IPM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BajoRend" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin Conv" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda NC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda No Convertida" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Corp" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Destino" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por País" sheetId="8" state="visible" r:id="rId8"/>
@@ -537,14 +537,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · P80 · target &lt;3%</t>
+          <t>CUG · P80 · target &lt;3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.001343784994400896</v>
+        <v>0.001275142939410144</v>
       </c>
     </row>
     <row r="7">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01773796192609182</v>
+        <v>0.01641232363950475</v>
       </c>
     </row>
     <row r="8">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1869</v>
+        <v>2013</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.08371780515117581</v>
+        <v>0.08280202377524577</v>
       </c>
     </row>
     <row r="9">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1429</v>
+        <v>1487</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06400895856662935</v>
+        <v>0.06116572744848011</v>
       </c>
     </row>
     <row r="10">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>18601</v>
+        <v>20381</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8331914893617022</v>
+        <v>0.8383447821973592</v>
       </c>
     </row>
   </sheetData>
@@ -690,14 +690,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · P80 · target ≥ $650</t>
+          <t>CUG · P80 · target ≥ $650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>17865</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.8002239641657335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1062</v>
+        <v>20673</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.04756998880179171</v>
+        <v>0.8503558060137386</v>
       </c>
     </row>
     <row r="8">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>427</v>
+        <v>473</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.01912653975363942</v>
+        <v>0.01945621323680638</v>
       </c>
     </row>
     <row r="9">
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>840</v>
+        <v>978</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.03762597984322508</v>
+        <v>0.04022870305622969</v>
       </c>
     </row>
     <row r="10">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2131</v>
+        <v>2187</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.09545352743561031</v>
+        <v>0.08995927769322529</v>
       </c>
     </row>
   </sheetData>
@@ -851,14 +851,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · BKGS&gt;0 · ordenado por tráfico ↓</t>
+          <t>CUG · BKGS&gt;0 · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3459,14 +3459,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
+          <t>CUG · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5504,14 +5504,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · tráfico × %NoDispo · ordenado por demanda perdida ↓</t>
+          <t>CUG · tráfico × %NoDispo · ordenado por demanda perdida ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7857,14 +7857,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · Top 50 corp · ordenado por tráfico ↓</t>
+          <t>CUG · Top 50 corp · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
         <v>22972.57</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.0138060554370632</v>
+        <v>0.01380605543706321</v>
       </c>
       <c r="G38" s="15" t="n">
         <v>2492.107671741196</v>
@@ -9089,7 +9089,7 @@
         <v>-3917.62</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.01237220616210537</v>
+        <v>0.01237220616210536</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>-448.1121473391075</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -9700,14 +9700,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · Top 50 destinos · ordenado por tráfico ↓</t>
+          <t>CUG · Top 50 destinos · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10127,7 @@
         <v>132249.45</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.05027503091966413</v>
+        <v>0.05027503091966414</v>
       </c>
       <c r="G16" s="15" t="n">
         <v>1597.05849704831</v>
@@ -10932,7 +10932,7 @@
         <v>71302.23999999999</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.05482390586902029</v>
+        <v>0.05482390586902028</v>
       </c>
       <c r="G39" s="15" t="n">
         <v>2342.447665269028</v>
@@ -11519,7 +11519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11530,7 +11530,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11543,14 +11543,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG (UOP) · todos los países · ordenado por tráfico ↓</t>
+          <t>CUG · todos los países · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13860,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>0.02394806509505192</v>
+        <v>0.02394806509505193</v>
       </c>
       <c r="G70" s="15" t="n">
         <v>0</v>
@@ -13872,7 +13872,7 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13965,7 +13965,7 @@
         <v>-404.21</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.02363224965867728</v>
+        <v>0.02363224965867727</v>
       </c>
       <c r="G73" s="15" t="n">
         <v>-484.9422090838634</v>
@@ -14117,7 +14117,7 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14700,7 +14700,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>0.005989277370389877</v>
+        <v>0.005989277370389876</v>
       </c>
       <c r="G94" s="15" t="n">
         <v>0</v>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
         <v>621.1</v>
       </c>
       <c r="F104" s="14" t="n">
-        <v>0.09683485707672723</v>
+        <v>0.09683485707672725</v>
       </c>
       <c r="G104" s="15" t="n">
         <v>1996.618189767131</v>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15517,7 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15867,7 +15867,7 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16135,7 +16135,7 @@
         <v>0</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>0.1979078506381394</v>
+        <v>0.1979078506381395</v>
       </c>
       <c r="G135" s="15" t="n">
         <v>0</v>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16497,7 +16497,7 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16672,7 +16672,7 @@
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16847,7 +16847,7 @@
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16917,7 +16917,7 @@
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17197,7 +17197,7 @@
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17232,7 +17232,7 @@
       </c>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17267,7 +17267,7 @@
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,42 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -544,7 +544,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
@@ -858,7 +858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
         <v>0.005784213013209309</v>
       </c>
       <c r="J6" s="15" t="n">
-        <v>-815.6840989980536</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>0.09407428117251154</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>-424.1892292326012</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>0.01027767780363369</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>-813.0517084589115</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>0.03124109504822978</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>-3421.649887026313</v>
+        <v>0</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>0.03372309667800081</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>-1078.080859168198</v>
+        <v>0</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>0.1511592593898871</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>-713.7959092967661</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>0.02122696151664523</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>-713.3041998545989</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>0.001627281247601508</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>-1262.559090740388</v>
+        <v>0</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>0.1197295911477005</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>-488.7554729391683</v>
+        <v>0</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>0.03905730671454677</v>
       </c>
       <c r="J22" s="15" t="n">
-        <v>-4132.899169648977</v>
+        <v>0</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>0.2551093076715465</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>-693.7951958603617</v>
+        <v>0</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>0.02400452846223347</v>
       </c>
       <c r="J24" s="15" t="n">
-        <v>-1433.890419772383</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>0.0321491184259477</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>-106.2159681426815</v>
+        <v>0</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>0.04798990742499561</v>
       </c>
       <c r="J32" s="15" t="n">
-        <v>-1193.846014161622</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>0.004471737680488874</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>-446.4406962979877</v>
+        <v>0</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>0.04092556107624056</v>
       </c>
       <c r="J36" s="15" t="n">
-        <v>-1030.421384809308</v>
+        <v>0</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>0.006502633720432467</v>
       </c>
       <c r="J38" s="15" t="n">
-        <v>-791.8824721478973</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>0.02984675899927653</v>
       </c>
       <c r="J40" s="15" t="n">
-        <v>-3162.573678474253</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>0.3919601236662269</v>
       </c>
       <c r="J44" s="15" t="n">
-        <v>-4620.182984805399</v>
+        <v>0</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>0.08158339214919015</v>
       </c>
       <c r="J48" s="15" t="n">
-        <v>-2797.297211812092</v>
+        <v>0</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>0.003487099586370634</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>-543.689856240836</v>
+        <v>0</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -5511,7 +5511,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5609,7 @@
         <v>8</v>
       </c>
       <c r="J6" s="15" t="n">
-        <v>-4620.182984805399</v>
+        <v>0</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-693.7951958603617</v>
+        <v>0</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>9</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>-713.7959092967661</v>
+        <v>0</v>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>9</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>-649.7922632433995</v>
+        <v>0</v>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>3</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>-424.1892292326012</v>
+        <v>0</v>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>-291.0102656423374</v>
+        <v>0</v>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>3</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>-2093.325428629065</v>
+        <v>0</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>11</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>-488.7554729391683</v>
+        <v>0</v>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="15" t="n">
-        <v>-1986.069089337367</v>
+        <v>0</v>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>18</v>
       </c>
       <c r="J52" s="15" t="n">
-        <v>-5377.112770960232</v>
+        <v>0</v>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -7864,7 +7864,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
         <v>0.05752943128902078</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>-270.7074322570051</v>
+        <v>0</v>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>0.007488078343480818</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>-968.6855100148371</v>
+        <v>0</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>0.01237220616210536</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>-448.1121473391075</v>
+        <v>0</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>0.1333748985093365</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>-73.25617321247427</v>
+        <v>0</v>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>0.07720377301715224</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>-3952.343174073519</v>
+        <v>0</v>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -9707,7 +9707,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10445,7 @@
         <v>0.07258547325541587</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>-3.865904621567378</v>
+        <v>0</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>0.04085863950811535</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>-453.7964173754067</v>
+        <v>0</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -11550,7 +11550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12638,7 @@
         <v>0.02380459704513859</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>-99.56592188480941</v>
+        <v>0</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>0.0372430907252571</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>-75.4839063195496</v>
+        <v>0</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>0.04421912606482368</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>-1411.866559265266</v>
+        <v>0</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>0.02691189705543784</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>-151.3914760320085</v>
+        <v>0</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>0.03051657823259954</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>-1112.059467252782</v>
+        <v>0</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>0.01659892533633349</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>-510.473050890078</v>
+        <v>0</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>0.00710004145634174</v>
       </c>
       <c r="G67" s="15" t="n">
-        <v>-746.7387849279967</v>
+        <v>0</v>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>0.01041071747144686</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>-1377.531289025224</v>
+        <v>0</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>0.02363224965867727</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>-484.9422090838634</v>
+        <v>0</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>0.01073702591622479</v>
       </c>
       <c r="G91" s="15" t="n">
-        <v>-6078.962499201431</v>
+        <v>0</v>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>0.003531671852057878</v>
       </c>
       <c r="G93" s="15" t="n">
-        <v>-20.52595606324257</v>
+        <v>0</v>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>0.1026081524285491</v>
       </c>
       <c r="G153" s="15" t="n">
-        <v>-42198.96923317195</v>
+        <v>0</v>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
